--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\CAER_calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE86BA22-F752-4CEE-855F-CAD3EFA5877A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D5FA40-40C9-461F-8B5D-012D06D23BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="264" windowWidth="23016" windowHeight="11976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>AMZN</t>
   </si>
@@ -58,19 +58,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Fee1</t>
+    <t>Cost1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Fee2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Price1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Price2</t>
+    <t>Cost2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -423,17 +415,12 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
@@ -452,13 +439,7 @@
         <v>1000</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
-      </c>
-      <c r="G2">
         <v>1000</v>
-      </c>
-      <c r="H2">
-        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -478,13 +459,7 @@
         <v>1000</v>
       </c>
       <c r="F3">
-        <v>0.1</v>
-      </c>
-      <c r="G3">
         <v>1000</v>
-      </c>
-      <c r="H3">
-        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -504,13 +479,7 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>1.2</v>
-      </c>
-      <c r="G4">
         <v>20</v>
-      </c>
-      <c r="H4">
-        <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -530,13 +499,7 @@
         <v>1005</v>
       </c>
       <c r="F5">
-        <v>0.1</v>
-      </c>
-      <c r="G5">
         <v>1005</v>
-      </c>
-      <c r="H5">
-        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -553,16 +516,10 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="F6">
-        <v>0.1</v>
-      </c>
-      <c r="G6">
-        <v>900</v>
-      </c>
-      <c r="H6">
-        <v>0.1</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
